--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B366BC7-EB5A-4B42-B49E-1583D548436F}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB0E9AC3-6BC2-4B24-A84C-F21A0658BAF2}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
-    <sheet name="Contract_List" sheetId="1" r:id="rId1"/>
-    <sheet name="Contract_List_Course" sheetId="2" r:id="rId2"/>
+    <sheet name="Contract" sheetId="1" r:id="rId1"/>
+    <sheet name="Contract_Course" sheetId="2" r:id="rId2"/>
     <sheet name="Contract_Asset" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB0E9AC3-6BC2-4B24-A84C-F21A0658BAF2}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{971E0DFB-43DE-49AF-8203-80275852D880}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
-    <sheet name="Contract" sheetId="1" r:id="rId1"/>
-    <sheet name="Contract_Course" sheetId="2" r:id="rId2"/>
-    <sheet name="Contract_Asset" sheetId="3" r:id="rId3"/>
+    <sheet name="合同" sheetId="1" r:id="rId1"/>
+    <sheet name="相关课程" sheetId="2" r:id="rId2"/>
+    <sheet name="相关设备" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{971E0DFB-43DE-49AF-8203-80275852D880}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5FD89E4-A34A-447A-B68B-E220B608DE86}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
@@ -105,19 +105,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="7"/>
-      <color rgb="FF172B4D"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
@@ -127,30 +121,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
+      <sz val="12"/>
       <color rgb="FF172B4D"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
+      <name val="宋体"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4F5F7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -180,27 +161,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -518,11 +486,16 @@
   <dimension ref="A1:L1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.44140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.6640625" customWidth="1"/>
-    <col min="11" max="11" width="10.77734375" customWidth="1"/>
+    <col min="9" max="9" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>14</v>
       </c>
@@ -541,7 +514,7 @@
       <c r="F1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="3" t="s">
@@ -571,29 +544,37 @@
   <dimension ref="A1:J1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="5" max="6" width="8.88671875" style="5"/>
+    <col min="1" max="1" width="15.88671875" customWidth="1"/>
+    <col min="2" max="2" width="13.21875" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" customWidth="1"/>
+    <col min="4" max="4" width="15.5546875" customWidth="1"/>
+    <col min="5" max="5" width="16.44140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.77734375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.88671875" customWidth="1"/>
+    <col min="9" max="9" width="15.109375" customWidth="1"/>
+    <col min="10" max="10" width="15.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="3" t="s">
@@ -618,47 +599,52 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.44140625" customWidth="1"/>
-    <col min="2" max="2" width="12.88671875" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" customWidth="1"/>
     <col min="3" max="3" width="20.33203125" customWidth="1"/>
+    <col min="4" max="4" width="10.5546875" customWidth="1"/>
     <col min="5" max="5" width="12.6640625" customWidth="1"/>
+    <col min="8" max="8" width="12.44140625" customWidth="1"/>
+    <col min="9" max="9" width="13.5546875" customWidth="1"/>
+    <col min="10" max="10" width="12.44140625" customWidth="1"/>
+    <col min="11" max="11" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5FD89E4-A34A-447A-B68B-E220B608DE86}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B295855-0BEF-43E9-AA16-41FFD17508EF}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-28920" yWindow="1155" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
     <sheet name="合同" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="37">
   <si>
     <t>代理商</t>
   </si>
@@ -53,30 +53,15 @@
     <t>IB数量</t>
   </si>
   <si>
-    <t>备件名额</t>
-  </si>
-  <si>
-    <t>探头名额</t>
-  </si>
-  <si>
-    <t>人工支持次数</t>
-  </si>
-  <si>
     <t>课程名称</t>
   </si>
   <si>
-    <t>备件+人工+保养</t>
-  </si>
-  <si>
     <t>合同号</t>
   </si>
   <si>
     <t>课程ID</t>
   </si>
   <si>
-    <t>课程额度</t>
-  </si>
-  <si>
     <t>区域</t>
   </si>
   <si>
@@ -99,6 +84,66 @@
   </si>
   <si>
     <t>备注</t>
+  </si>
+  <si>
+    <t>备件总额</t>
+  </si>
+  <si>
+    <t>备件剩余名额</t>
+  </si>
+  <si>
+    <t>备件申请名额</t>
+  </si>
+  <si>
+    <t>备件已使用名额</t>
+  </si>
+  <si>
+    <t>探头总额</t>
+  </si>
+  <si>
+    <t>探头剩余名额</t>
+  </si>
+  <si>
+    <t>探头申请名额</t>
+  </si>
+  <si>
+    <t>探头已使用名额</t>
+  </si>
+  <si>
+    <t>人工支持总次数</t>
+  </si>
+  <si>
+    <t>人工支持剩余次数</t>
+  </si>
+  <si>
+    <t>人工支持申请次数</t>
+  </si>
+  <si>
+    <t>人工支持已使用次数</t>
+  </si>
+  <si>
+    <t>备件+人工+保养总额</t>
+  </si>
+  <si>
+    <t>备件+人工+保养剩余名额</t>
+  </si>
+  <si>
+    <t>备件+人工+保养申请名额</t>
+  </si>
+  <si>
+    <t>备件+人工+保养已使用名额</t>
+  </si>
+  <si>
+    <t>课程总额</t>
+  </si>
+  <si>
+    <t>课程剩余名额</t>
+  </si>
+  <si>
+    <t>课程申请名额</t>
+  </si>
+  <si>
+    <t>课程已使用名额</t>
   </si>
 </sst>
 </file>
@@ -483,27 +528,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:X1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="14.44140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.6640625" customWidth="1"/>
     <col min="9" max="9" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.21875" customWidth="1"/>
+    <col min="14" max="14" width="16.88671875" customWidth="1"/>
+    <col min="15" max="15" width="14.6640625" customWidth="1"/>
+    <col min="16" max="17" width="16.77734375" customWidth="1"/>
+    <col min="18" max="18" width="19.44140625" customWidth="1"/>
+    <col min="19" max="19" width="19.33203125" customWidth="1"/>
+    <col min="20" max="20" width="21.21875" customWidth="1"/>
+    <col min="21" max="21" width="23.21875" customWidth="1"/>
+    <col min="22" max="22" width="26.5546875" customWidth="1"/>
+    <col min="23" max="23" width="24.88671875" customWidth="1"/>
+    <col min="24" max="24" width="29.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>1</v>
@@ -521,16 +576,52 @@
         <v>5</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>7</v>
+        <v>20</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="S1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="U1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="V1" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="W1" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="X1" s="3" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -541,7 +632,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD4DBF4-FEF1-4385-BAD9-BD07A4FA541B}">
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.88671875" customWidth="1"/>
@@ -553,17 +644,20 @@
     <col min="7" max="7" width="16.88671875" customWidth="1"/>
     <col min="9" max="9" width="15.109375" customWidth="1"/>
     <col min="10" max="10" width="15.88671875" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="12" max="12" width="17.33203125" customWidth="1"/>
+    <col min="13" max="13" width="21.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>1</v>
@@ -578,13 +672,22 @@
         <v>4</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>13</v>
+        <v>33</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -611,7 +714,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>2</v>
@@ -623,30 +726,31 @@
         <v>4</v>
       </c>
       <c r="E1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>16</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>21</v>
       </c>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B295855-0BEF-43E9-AA16-41FFD17508EF}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5FD89E4-A34A-447A-B68B-E220B608DE86}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1155" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
     <sheet name="合同" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="22">
   <si>
     <t>代理商</t>
   </si>
@@ -53,15 +53,30 @@
     <t>IB数量</t>
   </si>
   <si>
+    <t>备件名额</t>
+  </si>
+  <si>
+    <t>探头名额</t>
+  </si>
+  <si>
+    <t>人工支持次数</t>
+  </si>
+  <si>
     <t>课程名称</t>
   </si>
   <si>
+    <t>备件+人工+保养</t>
+  </si>
+  <si>
     <t>合同号</t>
   </si>
   <si>
     <t>课程ID</t>
   </si>
   <si>
+    <t>课程额度</t>
+  </si>
+  <si>
     <t>区域</t>
   </si>
   <si>
@@ -84,66 +99,6 @@
   </si>
   <si>
     <t>备注</t>
-  </si>
-  <si>
-    <t>备件总额</t>
-  </si>
-  <si>
-    <t>备件剩余名额</t>
-  </si>
-  <si>
-    <t>备件申请名额</t>
-  </si>
-  <si>
-    <t>备件已使用名额</t>
-  </si>
-  <si>
-    <t>探头总额</t>
-  </si>
-  <si>
-    <t>探头剩余名额</t>
-  </si>
-  <si>
-    <t>探头申请名额</t>
-  </si>
-  <si>
-    <t>探头已使用名额</t>
-  </si>
-  <si>
-    <t>人工支持总次数</t>
-  </si>
-  <si>
-    <t>人工支持剩余次数</t>
-  </si>
-  <si>
-    <t>人工支持申请次数</t>
-  </si>
-  <si>
-    <t>人工支持已使用次数</t>
-  </si>
-  <si>
-    <t>备件+人工+保养总额</t>
-  </si>
-  <si>
-    <t>备件+人工+保养剩余名额</t>
-  </si>
-  <si>
-    <t>备件+人工+保养申请名额</t>
-  </si>
-  <si>
-    <t>备件+人工+保养已使用名额</t>
-  </si>
-  <si>
-    <t>课程总额</t>
-  </si>
-  <si>
-    <t>课程剩余名额</t>
-  </si>
-  <si>
-    <t>课程申请名额</t>
-  </si>
-  <si>
-    <t>课程已使用名额</t>
   </si>
 </sst>
 </file>
@@ -528,37 +483,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
-  <dimension ref="A1:X1"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="14.44140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.6640625" customWidth="1"/>
     <col min="9" max="9" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.77734375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.21875" customWidth="1"/>
-    <col min="14" max="14" width="16.88671875" customWidth="1"/>
-    <col min="15" max="15" width="14.6640625" customWidth="1"/>
-    <col min="16" max="17" width="16.77734375" customWidth="1"/>
-    <col min="18" max="18" width="19.44140625" customWidth="1"/>
-    <col min="19" max="19" width="19.33203125" customWidth="1"/>
-    <col min="20" max="20" width="21.21875" customWidth="1"/>
-    <col min="21" max="21" width="23.21875" customWidth="1"/>
-    <col min="22" max="22" width="26.5546875" customWidth="1"/>
-    <col min="23" max="23" width="24.88671875" customWidth="1"/>
-    <col min="24" max="24" width="29.109375" customWidth="1"/>
+    <col min="10" max="10" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>1</v>
@@ -576,52 +521,16 @@
         <v>5</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="R1" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="S1" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="T1" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="U1" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="V1" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="W1" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="X1" s="3" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -632,7 +541,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD4DBF4-FEF1-4385-BAD9-BD07A4FA541B}">
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.88671875" customWidth="1"/>
@@ -644,20 +553,17 @@
     <col min="7" max="7" width="16.88671875" customWidth="1"/>
     <col min="9" max="9" width="15.109375" customWidth="1"/>
     <col min="10" max="10" width="15.88671875" customWidth="1"/>
-    <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="17.33203125" customWidth="1"/>
-    <col min="13" max="13" width="21.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>1</v>
@@ -672,22 +578,13 @@
         <v>4</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -714,7 +611,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>2</v>
@@ -726,31 +623,30 @@
         <v>4</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B295855-0BEF-43E9-AA16-41FFD17508EF}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35FC1DB9-6247-4D81-A3F2-DB427D990C8E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1155" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
     <sheet name="合同" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="37">
   <si>
     <t>代理商</t>
   </si>
@@ -528,29 +528,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
-  <dimension ref="A1:X1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:Y1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.6640625" customWidth="1"/>
-    <col min="9" max="9" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.77734375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.21875" customWidth="1"/>
-    <col min="14" max="14" width="16.88671875" customWidth="1"/>
-    <col min="15" max="15" width="14.6640625" customWidth="1"/>
-    <col min="16" max="17" width="16.77734375" customWidth="1"/>
-    <col min="18" max="18" width="19.44140625" customWidth="1"/>
-    <col min="19" max="19" width="19.33203125" customWidth="1"/>
-    <col min="20" max="20" width="21.21875" customWidth="1"/>
-    <col min="21" max="21" width="23.21875" customWidth="1"/>
-    <col min="22" max="22" width="26.5546875" customWidth="1"/>
-    <col min="23" max="23" width="24.88671875" customWidth="1"/>
-    <col min="24" max="24" width="29.109375" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.28515625" customWidth="1"/>
+    <col min="14" max="14" width="16.85546875" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" customWidth="1"/>
+    <col min="16" max="17" width="16.7109375" customWidth="1"/>
+    <col min="18" max="18" width="19.42578125" customWidth="1"/>
+    <col min="19" max="19" width="19.28515625" customWidth="1"/>
+    <col min="20" max="20" width="21.28515625" customWidth="1"/>
+    <col min="21" max="21" width="23.28515625" customWidth="1"/>
+    <col min="22" max="22" width="26.5703125" customWidth="1"/>
+    <col min="23" max="23" width="24.85546875" customWidth="1"/>
+    <col min="24" max="24" width="29.140625" customWidth="1"/>
+    <col min="25" max="25" width="27.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="4" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>9</v>
       </c>
@@ -622,6 +623,9 @@
       </c>
       <c r="X1" s="3" t="s">
         <v>32</v>
+      </c>
+      <c r="Y1" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -633,23 +637,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD4DBF4-FEF1-4385-BAD9-BD07A4FA541B}">
   <dimension ref="A1:M1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.88671875" customWidth="1"/>
-    <col min="2" max="2" width="13.21875" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" customWidth="1"/>
-    <col min="4" max="4" width="15.5546875" customWidth="1"/>
-    <col min="5" max="5" width="16.44140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.77734375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.88671875" customWidth="1"/>
-    <col min="9" max="9" width="15.109375" customWidth="1"/>
-    <col min="10" max="10" width="15.88671875" customWidth="1"/>
+    <col min="1" max="1" width="15.85546875" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" customWidth="1"/>
+    <col min="5" max="5" width="16.42578125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.85546875" customWidth="1"/>
+    <col min="9" max="9" width="15.140625" customWidth="1"/>
+    <col min="10" max="10" width="15.85546875" customWidth="1"/>
     <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="17.33203125" customWidth="1"/>
-    <col min="13" max="13" width="21.5546875" customWidth="1"/>
+    <col min="12" max="12" width="17.28515625" customWidth="1"/>
+    <col min="13" max="13" width="21.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>9</v>
       </c>
@@ -699,20 +703,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1A9004E-0524-4CCC-A26D-ED41880F2076}">
   <dimension ref="A1:M1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.44140625" customWidth="1"/>
-    <col min="2" max="2" width="17.6640625" customWidth="1"/>
-    <col min="3" max="3" width="20.33203125" customWidth="1"/>
-    <col min="4" max="4" width="10.5546875" customWidth="1"/>
-    <col min="5" max="5" width="12.6640625" customWidth="1"/>
-    <col min="8" max="8" width="12.44140625" customWidth="1"/>
-    <col min="9" max="9" width="13.5546875" customWidth="1"/>
-    <col min="10" max="10" width="12.44140625" customWidth="1"/>
-    <col min="11" max="11" width="12.6640625" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="20.28515625" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" customWidth="1"/>
+    <col min="8" max="8" width="12.42578125" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" customWidth="1"/>
+    <col min="10" max="10" width="12.42578125" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>7</v>
       </c>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35FC1DB9-6247-4D81-A3F2-DB427D990C8E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2815618-E2B3-451B-ABF4-29160B673B60}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
     <sheet name="合同" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="38">
   <si>
     <t>代理商</t>
   </si>
@@ -144,6 +144,9 @@
   </si>
   <si>
     <t>课程已使用名额</t>
+  </si>
+  <si>
+    <t>高低端机</t>
   </si>
 </sst>
 </file>
@@ -702,7 +705,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1A9004E-0524-4CCC-A26D-ED41880F2076}">
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" customWidth="1"/>
@@ -712,11 +715,11 @@
     <col min="5" max="5" width="12.7109375" customWidth="1"/>
     <col min="8" max="8" width="12.42578125" customWidth="1"/>
     <col min="9" max="9" width="13.5703125" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" customWidth="1"/>
-    <col min="11" max="11" width="12.7109375" customWidth="1"/>
+    <col min="10" max="11" width="12.42578125" customWidth="1"/>
+    <col min="12" max="12" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>7</v>
       </c>
@@ -748,10 +751,13 @@
         <v>15</v>
       </c>
       <c r="K1" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="2"/>
       <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2815618-E2B3-451B-ABF4-29160B673B60}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3D5CB1A-C7A5-4A85-BC41-ED743882B154}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
     <sheet name="合同" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="41">
   <si>
     <t>代理商</t>
   </si>
@@ -101,9 +101,6 @@
     <t>探头总额</t>
   </si>
   <si>
-    <t>探头剩余名额</t>
-  </si>
-  <si>
     <t>探头申请名额</t>
   </si>
   <si>
@@ -147,6 +144,18 @@
   </si>
   <si>
     <t>高低端机</t>
+  </si>
+  <si>
+    <t>探头任意剩余名额</t>
+  </si>
+  <si>
+    <t>探头普通剩余名额</t>
+  </si>
+  <si>
+    <t>探头特殊剩余名额</t>
+  </si>
+  <si>
+    <t>探头高值剩余名额</t>
   </si>
 </sst>
 </file>
@@ -531,7 +540,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
-  <dimension ref="A1:Y1"/>
+  <dimension ref="A1:AB1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
@@ -541,20 +550,20 @@
     <col min="10" max="11" width="14.42578125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13.28515625" customWidth="1"/>
-    <col min="14" max="14" width="16.85546875" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" customWidth="1"/>
-    <col min="16" max="17" width="16.7109375" customWidth="1"/>
-    <col min="18" max="18" width="19.42578125" customWidth="1"/>
-    <col min="19" max="19" width="19.28515625" customWidth="1"/>
-    <col min="20" max="20" width="21.28515625" customWidth="1"/>
-    <col min="21" max="21" width="23.28515625" customWidth="1"/>
-    <col min="22" max="22" width="26.5703125" customWidth="1"/>
-    <col min="23" max="23" width="24.85546875" customWidth="1"/>
-    <col min="24" max="24" width="29.140625" customWidth="1"/>
-    <col min="25" max="25" width="27.85546875" customWidth="1"/>
+    <col min="14" max="17" width="19.140625" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" customWidth="1"/>
+    <col min="19" max="20" width="16.7109375" customWidth="1"/>
+    <col min="21" max="21" width="19.42578125" customWidth="1"/>
+    <col min="22" max="22" width="19.28515625" customWidth="1"/>
+    <col min="23" max="23" width="21.28515625" customWidth="1"/>
+    <col min="24" max="24" width="23.28515625" customWidth="1"/>
+    <col min="25" max="25" width="26.5703125" customWidth="1"/>
+    <col min="26" max="26" width="24.85546875" customWidth="1"/>
+    <col min="27" max="27" width="29.140625" customWidth="1"/>
+    <col min="28" max="28" width="27.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>9</v>
       </c>
@@ -595,39 +604,48 @@
         <v>21</v>
       </c>
       <c r="N1" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="R1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="W1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="Y1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="Z1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="AA1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="X1" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y1" s="3" t="s">
+      <c r="AB1" s="3" t="s">
         <v>16</v>
       </c>
     </row>
@@ -685,16 +703,16 @@
         <v>6</v>
       </c>
       <c r="J1" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -751,7 +769,7 @@
         <v>15</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>16</v>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503202755\Desktop\New folder (12)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3D5CB1A-C7A5-4A85-BC41-ED743882B154}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4F005C5-45C6-4C2C-AB80-A5066D03CA80}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
     <sheet name="合同" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="43">
   <si>
     <t>代理商</t>
   </si>
@@ -156,13 +156,19 @@
   </si>
   <si>
     <t>探头高值剩余名额</t>
+  </si>
+  <si>
+    <t>培训合同号</t>
+  </si>
+  <si>
+    <t>modality</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -228,7 +234,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -244,7 +250,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -541,29 +547,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
   <dimension ref="A1:AB1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.28515625" customWidth="1"/>
-    <col min="14" max="17" width="19.140625" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" customWidth="1"/>
-    <col min="19" max="20" width="16.7109375" customWidth="1"/>
-    <col min="21" max="21" width="19.42578125" customWidth="1"/>
-    <col min="22" max="22" width="19.28515625" customWidth="1"/>
-    <col min="23" max="23" width="21.28515625" customWidth="1"/>
-    <col min="24" max="24" width="23.28515625" customWidth="1"/>
-    <col min="25" max="25" width="26.5703125" customWidth="1"/>
-    <col min="26" max="26" width="24.85546875" customWidth="1"/>
-    <col min="27" max="27" width="29.140625" customWidth="1"/>
-    <col min="28" max="28" width="27.85546875" customWidth="1"/>
+    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" customWidth="1"/>
+    <col min="9" max="9" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.33203125" customWidth="1"/>
+    <col min="14" max="17" width="19.109375" customWidth="1"/>
+    <col min="18" max="18" width="14.6640625" customWidth="1"/>
+    <col min="19" max="20" width="16.6640625" customWidth="1"/>
+    <col min="21" max="21" width="19.44140625" customWidth="1"/>
+    <col min="22" max="22" width="19.33203125" customWidth="1"/>
+    <col min="23" max="23" width="21.33203125" customWidth="1"/>
+    <col min="24" max="24" width="23.33203125" customWidth="1"/>
+    <col min="25" max="25" width="26.5546875" customWidth="1"/>
+    <col min="26" max="26" width="24.88671875" customWidth="1"/>
+    <col min="27" max="27" width="29.109375" customWidth="1"/>
+    <col min="28" max="28" width="27.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" s="4" customFormat="1" ht="15.6">
       <c r="A1" s="3" t="s">
         <v>9</v>
       </c>
@@ -657,24 +663,25 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD4DBF4-FEF1-4385-BAD9-BD07A4FA541B}">
-  <dimension ref="A1:M1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O1"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="15.85546875" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" customWidth="1"/>
-    <col min="5" max="5" width="16.42578125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="16.85546875" customWidth="1"/>
-    <col min="9" max="9" width="15.140625" customWidth="1"/>
-    <col min="10" max="10" width="15.85546875" customWidth="1"/>
-    <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="17.28515625" customWidth="1"/>
-    <col min="13" max="13" width="21.5703125" customWidth="1"/>
+    <col min="1" max="1" width="15.88671875" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" customWidth="1"/>
+    <col min="4" max="4" width="15.5546875" customWidth="1"/>
+    <col min="5" max="5" width="16.44140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" style="1" customWidth="1"/>
+    <col min="7" max="8" width="16.88671875" customWidth="1"/>
+    <col min="10" max="10" width="19.33203125" customWidth="1"/>
+    <col min="11" max="11" width="15.109375" customWidth="1"/>
+    <col min="12" max="12" width="15.88671875" customWidth="1"/>
+    <col min="13" max="13" width="16" customWidth="1"/>
+    <col min="14" max="14" width="17.33203125" customWidth="1"/>
+    <col min="15" max="15" width="21.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="15.6">
       <c r="A1" s="3" t="s">
         <v>9</v>
       </c>
@@ -697,21 +704,27 @@
         <v>4</v>
       </c>
       <c r="H1" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>35</v>
       </c>
     </row>
@@ -724,20 +737,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1A9004E-0524-4CCC-A26D-ED41880F2076}">
   <dimension ref="A1:N1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" customWidth="1"/>
-    <col min="2" max="2" width="17.7109375" customWidth="1"/>
-    <col min="3" max="3" width="20.28515625" customWidth="1"/>
-    <col min="4" max="4" width="10.5703125" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" customWidth="1"/>
-    <col min="8" max="8" width="12.42578125" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" customWidth="1"/>
-    <col min="10" max="11" width="12.42578125" customWidth="1"/>
-    <col min="12" max="12" width="12.7109375" customWidth="1"/>
+    <col min="1" max="1" width="11.44140625" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" customWidth="1"/>
+    <col min="3" max="3" width="20.33203125" customWidth="1"/>
+    <col min="4" max="4" width="10.5546875" customWidth="1"/>
+    <col min="5" max="5" width="12.6640625" customWidth="1"/>
+    <col min="8" max="8" width="12.44140625" customWidth="1"/>
+    <col min="9" max="9" width="13.5546875" customWidth="1"/>
+    <col min="10" max="11" width="12.44140625" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="15.6">
       <c r="A1" s="3" t="s">
         <v>7</v>
       </c>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503202755\Desktop\New folder (12)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4F005C5-45C6-4C2C-AB80-A5066D03CA80}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E55C93A-1B0B-4D5C-938A-78648AE025B9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
     <sheet name="合同" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="51">
   <si>
     <t>代理商</t>
   </si>
@@ -92,83 +92,107 @@
     <t>备件剩余名额</t>
   </si>
   <si>
-    <t>备件申请名额</t>
-  </si>
-  <si>
     <t>备件已使用名额</t>
   </si>
   <si>
-    <t>探头总额</t>
-  </si>
-  <si>
-    <t>探头申请名额</t>
-  </si>
-  <si>
-    <t>探头已使用名额</t>
-  </si>
-  <si>
     <t>人工支持总次数</t>
   </si>
   <si>
     <t>人工支持剩余次数</t>
   </si>
   <si>
+    <t>人工支持已使用次数</t>
+  </si>
+  <si>
+    <t>备件+人工+保养总额</t>
+  </si>
+  <si>
+    <t>备件+人工+保养剩余名额</t>
+  </si>
+  <si>
+    <t>备件+人工+保养已使用名额</t>
+  </si>
+  <si>
+    <t>课程总额</t>
+  </si>
+  <si>
+    <t>课程剩余名额</t>
+  </si>
+  <si>
+    <t>课程申请名额</t>
+  </si>
+  <si>
+    <t>课程已使用名额</t>
+  </si>
+  <si>
+    <t>高低端机</t>
+  </si>
+  <si>
+    <t>探头任意剩余名额</t>
+  </si>
+  <si>
+    <t>探头普通剩余名额</t>
+  </si>
+  <si>
+    <t>探头特殊剩余名额</t>
+  </si>
+  <si>
+    <t>探头高值剩余名额</t>
+  </si>
+  <si>
+    <t>培训合同号</t>
+  </si>
+  <si>
+    <t>modality</t>
+  </si>
+  <si>
+    <t>探头任意总额</t>
+  </si>
+  <si>
+    <t>探头任意已使用名额</t>
+  </si>
+  <si>
+    <t>探头普通总额</t>
+  </si>
+  <si>
+    <t>探头普通已使用名额</t>
+  </si>
+  <si>
+    <t>探头特殊总额</t>
+  </si>
+  <si>
+    <t>探头特殊已使用名额</t>
+  </si>
+  <si>
+    <t>探头高值总额</t>
+  </si>
+  <si>
+    <t>探头高值已使用名额</t>
+  </si>
+  <si>
+    <t>探头任意申请名额</t>
+  </si>
+  <si>
+    <t>探头普通申请名额</t>
+  </si>
+  <si>
+    <t>探头特殊申请名额</t>
+  </si>
+  <si>
+    <t>探头高值申请名额</t>
+  </si>
+  <si>
     <t>人工支持申请次数</t>
   </si>
   <si>
-    <t>人工支持已使用次数</t>
-  </si>
-  <si>
-    <t>备件+人工+保养总额</t>
-  </si>
-  <si>
-    <t>备件+人工+保养剩余名额</t>
-  </si>
-  <si>
     <t>备件+人工+保养申请名额</t>
-  </si>
-  <si>
-    <t>备件+人工+保养已使用名额</t>
-  </si>
-  <si>
-    <t>课程总额</t>
-  </si>
-  <si>
-    <t>课程剩余名额</t>
-  </si>
-  <si>
-    <t>课程申请名额</t>
-  </si>
-  <si>
-    <t>课程已使用名额</t>
-  </si>
-  <si>
-    <t>高低端机</t>
-  </si>
-  <si>
-    <t>探头任意剩余名额</t>
-  </si>
-  <si>
-    <t>探头普通剩余名额</t>
-  </si>
-  <si>
-    <t>探头特殊剩余名额</t>
-  </si>
-  <si>
-    <t>探头高值剩余名额</t>
-  </si>
-  <si>
-    <t>培训合同号</t>
-  </si>
-  <si>
-    <t>modality</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -234,7 +258,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -250,7 +274,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -546,30 +570,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
-  <dimension ref="A1:AB1"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:AJ1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.6640625" customWidth="1"/>
-    <col min="9" max="9" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.33203125" customWidth="1"/>
-    <col min="14" max="17" width="19.109375" customWidth="1"/>
-    <col min="18" max="18" width="14.6640625" customWidth="1"/>
-    <col min="19" max="20" width="16.6640625" customWidth="1"/>
-    <col min="21" max="21" width="19.44140625" customWidth="1"/>
-    <col min="22" max="22" width="19.33203125" customWidth="1"/>
-    <col min="23" max="23" width="21.33203125" customWidth="1"/>
-    <col min="24" max="24" width="23.33203125" customWidth="1"/>
-    <col min="25" max="25" width="26.5546875" customWidth="1"/>
-    <col min="26" max="26" width="24.88671875" customWidth="1"/>
-    <col min="27" max="27" width="29.109375" customWidth="1"/>
-    <col min="28" max="28" width="27.88671875" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.28515625" customWidth="1"/>
+    <col min="13" max="13" width="16.7109375" customWidth="1"/>
+    <col min="14" max="18" width="19.140625" customWidth="1"/>
+    <col min="19" max="19" width="21.42578125" customWidth="1"/>
+    <col min="20" max="27" width="19.140625" customWidth="1"/>
+    <col min="28" max="28" width="16.7109375" customWidth="1"/>
+    <col min="29" max="30" width="19.42578125" customWidth="1"/>
+    <col min="31" max="31" width="21.28515625" customWidth="1"/>
+    <col min="32" max="32" width="23.28515625" customWidth="1"/>
+    <col min="33" max="34" width="26.5703125" customWidth="1"/>
+    <col min="35" max="35" width="29.140625" customWidth="1"/>
+    <col min="36" max="36" width="27.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" s="4" customFormat="1" ht="15.6">
+    <row r="1" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>9</v>
       </c>
@@ -604,54 +628,78 @@
         <v>19</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="P1" s="3" t="s">
         <v>39</v>
       </c>
       <c r="Q1" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="T1" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="U1" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="V1" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="W1" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="X1" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y1" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z1" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA1" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="AC1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AD1" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="AF1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="AG1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="AH1" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AI1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="V1" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="W1" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y1" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="Z1" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA1" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AJ1" s="3" t="s">
         <v>16</v>
       </c>
     </row>
@@ -664,24 +712,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD4DBF4-FEF1-4385-BAD9-BD07A4FA541B}">
   <dimension ref="A1:O1"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.88671875" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" customWidth="1"/>
-    <col min="4" max="4" width="15.5546875" customWidth="1"/>
-    <col min="5" max="5" width="16.44140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" style="1" customWidth="1"/>
-    <col min="7" max="8" width="16.88671875" customWidth="1"/>
-    <col min="10" max="10" width="19.33203125" customWidth="1"/>
-    <col min="11" max="11" width="15.109375" customWidth="1"/>
-    <col min="12" max="12" width="15.88671875" customWidth="1"/>
+    <col min="1" max="1" width="15.85546875" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" customWidth="1"/>
+    <col min="5" max="5" width="16.42578125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.7109375" style="1" customWidth="1"/>
+    <col min="7" max="8" width="16.85546875" customWidth="1"/>
+    <col min="10" max="10" width="19.28515625" customWidth="1"/>
+    <col min="11" max="11" width="15.140625" customWidth="1"/>
+    <col min="12" max="12" width="15.85546875" customWidth="1"/>
     <col min="13" max="13" width="16" customWidth="1"/>
-    <col min="14" max="14" width="17.33203125" customWidth="1"/>
-    <col min="15" max="15" width="21.5546875" customWidth="1"/>
+    <col min="14" max="14" width="17.28515625" customWidth="1"/>
+    <col min="15" max="15" width="21.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.6">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>9</v>
       </c>
@@ -704,28 +752,28 @@
         <v>4</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>6</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -737,20 +785,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1A9004E-0524-4CCC-A26D-ED41880F2076}">
   <dimension ref="A1:N1"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.44140625" customWidth="1"/>
-    <col min="2" max="2" width="17.6640625" customWidth="1"/>
-    <col min="3" max="3" width="20.33203125" customWidth="1"/>
-    <col min="4" max="4" width="10.5546875" customWidth="1"/>
-    <col min="5" max="5" width="12.6640625" customWidth="1"/>
-    <col min="8" max="8" width="12.44140625" customWidth="1"/>
-    <col min="9" max="9" width="13.5546875" customWidth="1"/>
-    <col min="10" max="11" width="12.44140625" customWidth="1"/>
-    <col min="12" max="12" width="12.6640625" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="20.28515625" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" customWidth="1"/>
+    <col min="8" max="8" width="12.42578125" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" customWidth="1"/>
+    <col min="10" max="11" width="12.42578125" customWidth="1"/>
+    <col min="12" max="12" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15.6">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>7</v>
       </c>
@@ -782,7 +830,7 @@
         <v>15</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>16</v>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E55C93A-1B0B-4D5C-938A-78648AE025B9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C12D583-A738-4905-BDB9-3137A79EAD31}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="相关课程" sheetId="2" r:id="rId2"/>
     <sheet name="相关设备" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="47">
   <si>
     <t>代理商</t>
   </si>
@@ -137,9 +137,6 @@
     <t>探头特殊剩余名额</t>
   </si>
   <si>
-    <t>探头高值剩余名额</t>
-  </si>
-  <si>
     <t>培训合同号</t>
   </si>
   <si>
@@ -164,12 +161,6 @@
     <t>探头特殊已使用名额</t>
   </si>
   <si>
-    <t>探头高值总额</t>
-  </si>
-  <si>
-    <t>探头高值已使用名额</t>
-  </si>
-  <si>
     <t>探头任意申请名额</t>
   </si>
   <si>
@@ -177,9 +168,6 @@
   </si>
   <si>
     <t>探头特殊申请名额</t>
-  </si>
-  <si>
-    <t>探头高值申请名额</t>
   </si>
   <si>
     <t>人工支持申请次数</t>
@@ -570,7 +558,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
-  <dimension ref="A1:AJ1"/>
+  <dimension ref="A1:AF1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
@@ -583,17 +571,17 @@
     <col min="13" max="13" width="16.7109375" customWidth="1"/>
     <col min="14" max="18" width="19.140625" customWidth="1"/>
     <col min="19" max="19" width="21.42578125" customWidth="1"/>
-    <col min="20" max="27" width="19.140625" customWidth="1"/>
-    <col min="28" max="28" width="16.7109375" customWidth="1"/>
-    <col min="29" max="30" width="19.42578125" customWidth="1"/>
-    <col min="31" max="31" width="21.28515625" customWidth="1"/>
-    <col min="32" max="32" width="23.28515625" customWidth="1"/>
-    <col min="33" max="34" width="26.5703125" customWidth="1"/>
-    <col min="35" max="35" width="29.140625" customWidth="1"/>
-    <col min="36" max="36" width="27.85546875" customWidth="1"/>
+    <col min="20" max="23" width="19.140625" customWidth="1"/>
+    <col min="24" max="24" width="16.7109375" customWidth="1"/>
+    <col min="25" max="26" width="19.42578125" customWidth="1"/>
+    <col min="27" max="27" width="21.28515625" customWidth="1"/>
+    <col min="28" max="28" width="23.28515625" customWidth="1"/>
+    <col min="29" max="30" width="26.5703125" customWidth="1"/>
+    <col min="31" max="31" width="29.140625" customWidth="1"/>
+    <col min="32" max="32" width="27.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>9</v>
       </c>
@@ -628,78 +616,66 @@
         <v>19</v>
       </c>
       <c r="L1" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="M1" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>31</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q1" s="3" t="s">
         <v>32</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="S1" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T1" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="T1" s="3" t="s">
-        <v>41</v>
       </c>
       <c r="U1" s="3" t="s">
         <v>33</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="W1" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X1" s="3" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="Z1" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="AA1" s="3" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="AB1" s="3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AC1" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AD1" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="AE1" s="3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AF1" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="AG1" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="AH1" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="AI1" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="AJ1" s="3" t="s">
         <v>16</v>
       </c>
     </row>
@@ -752,13 +728,13 @@
         <v>4</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>6</v>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C12D583-A738-4905-BDB9-3137A79EAD31}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBABF639-1D06-4005-AB41-CA91138E1C1D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
     <sheet name="合同" sheetId="1" r:id="rId1"/>
     <sheet name="相关课程" sheetId="2" r:id="rId2"/>
     <sheet name="相关设备" sheetId="3" r:id="rId3"/>
+    <sheet name="相关高值探头" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="49">
   <si>
     <t>代理商</t>
   </si>
@@ -174,6 +175,12 @@
   </si>
   <si>
     <t>备件+人工+保养申请名额</t>
+  </si>
+  <si>
+    <t>SN编号</t>
+  </si>
+  <si>
+    <t>状态</t>
   </si>
 </sst>
 </file>
@@ -818,4 +825,42 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9A2251D-DDD2-48AF-A0F7-E61944EE8578}">
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" customWidth="1"/>
+    <col min="4" max="4" width="20.140625" customWidth="1"/>
+    <col min="5" max="5" width="27.85546875" customWidth="1"/>
+    <col min="6" max="6" width="19.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBABF639-1D06-4005-AB41-CA91138E1C1D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59A38B11-4455-4E9E-BAE8-305E80C0979A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
     <sheet name="合同" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="相关设备" sheetId="3" r:id="rId3"/>
     <sheet name="相关高值探头" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="50">
   <si>
     <t>代理商</t>
   </si>
@@ -181,6 +181,9 @@
   </si>
   <si>
     <t>状态</t>
+  </si>
+  <si>
+    <t>名额扣除类型</t>
   </si>
 </sst>
 </file>
@@ -565,30 +568,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AG1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="14.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.28515625" customWidth="1"/>
-    <col min="13" max="13" width="16.7109375" customWidth="1"/>
-    <col min="14" max="18" width="19.140625" customWidth="1"/>
-    <col min="19" max="19" width="21.42578125" customWidth="1"/>
-    <col min="20" max="23" width="19.140625" customWidth="1"/>
-    <col min="24" max="24" width="16.7109375" customWidth="1"/>
-    <col min="25" max="26" width="19.42578125" customWidth="1"/>
-    <col min="27" max="27" width="21.28515625" customWidth="1"/>
-    <col min="28" max="28" width="23.28515625" customWidth="1"/>
-    <col min="29" max="30" width="26.5703125" customWidth="1"/>
-    <col min="31" max="31" width="29.140625" customWidth="1"/>
-    <col min="32" max="32" width="27.85546875" customWidth="1"/>
+    <col min="8" max="8" width="17.7109375" customWidth="1"/>
+    <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.28515625" customWidth="1"/>
+    <col min="14" max="14" width="16.7109375" customWidth="1"/>
+    <col min="15" max="19" width="19.140625" customWidth="1"/>
+    <col min="20" max="20" width="21.42578125" customWidth="1"/>
+    <col min="21" max="24" width="19.140625" customWidth="1"/>
+    <col min="25" max="25" width="16.7109375" customWidth="1"/>
+    <col min="26" max="27" width="19.42578125" customWidth="1"/>
+    <col min="28" max="28" width="21.28515625" customWidth="1"/>
+    <col min="29" max="29" width="23.28515625" customWidth="1"/>
+    <col min="30" max="31" width="26.5703125" customWidth="1"/>
+    <col min="32" max="32" width="29.140625" customWidth="1"/>
+    <col min="33" max="33" width="27.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>9</v>
       </c>
@@ -611,78 +615,81 @@
         <v>4</v>
       </c>
       <c r="H1" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="W1" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="Y1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Z1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="AA1" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AB1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AC1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AD1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AE1" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AF1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AG1" s="3" t="s">
         <v>16</v>
       </c>
     </row>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59A38B11-4455-4E9E-BAE8-305E80C0979A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FFAD062-5796-495E-AFC2-3D63BE9D6DB4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="49">
   <si>
     <t>代理商</t>
   </si>
@@ -181,9 +181,6 @@
   </si>
   <si>
     <t>状态</t>
-  </si>
-  <si>
-    <t>名额扣除类型</t>
   </si>
 </sst>
 </file>
@@ -568,31 +565,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
-  <dimension ref="A1:AG1"/>
+  <dimension ref="A1:AF1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="14.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.7109375" customWidth="1"/>
-    <col min="8" max="8" width="17.7109375" customWidth="1"/>
-    <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.28515625" customWidth="1"/>
-    <col min="14" max="14" width="16.7109375" customWidth="1"/>
-    <col min="15" max="19" width="19.140625" customWidth="1"/>
-    <col min="20" max="20" width="21.42578125" customWidth="1"/>
-    <col min="21" max="24" width="19.140625" customWidth="1"/>
-    <col min="25" max="25" width="16.7109375" customWidth="1"/>
-    <col min="26" max="27" width="19.42578125" customWidth="1"/>
-    <col min="28" max="28" width="21.28515625" customWidth="1"/>
-    <col min="29" max="29" width="23.28515625" customWidth="1"/>
-    <col min="30" max="31" width="26.5703125" customWidth="1"/>
-    <col min="32" max="32" width="29.140625" customWidth="1"/>
-    <col min="33" max="33" width="27.85546875" customWidth="1"/>
+    <col min="9" max="9" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.28515625" customWidth="1"/>
+    <col min="13" max="13" width="16.7109375" customWidth="1"/>
+    <col min="14" max="18" width="19.140625" customWidth="1"/>
+    <col min="19" max="19" width="21.42578125" customWidth="1"/>
+    <col min="20" max="23" width="19.140625" customWidth="1"/>
+    <col min="24" max="24" width="16.7109375" customWidth="1"/>
+    <col min="25" max="26" width="19.42578125" customWidth="1"/>
+    <col min="27" max="27" width="21.28515625" customWidth="1"/>
+    <col min="28" max="28" width="23.28515625" customWidth="1"/>
+    <col min="29" max="30" width="26.5703125" customWidth="1"/>
+    <col min="31" max="31" width="29.140625" customWidth="1"/>
+    <col min="32" max="32" width="27.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>9</v>
       </c>
@@ -615,81 +611,78 @@
         <v>4</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="W1" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="X1" s="3" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z1" s="3" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="AA1" s="3" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="AB1" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AC1" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AD1" s="3" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="AE1" s="3" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="AF1" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG1" s="3" t="s">
         <v>16</v>
       </c>
     </row>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FFAD062-5796-495E-AFC2-3D63BE9D6DB4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{242EE13B-12BA-4F0D-AA6A-C24F768EC6AB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="50">
   <si>
     <t>代理商</t>
   </si>
@@ -181,6 +181,9 @@
   </si>
   <si>
     <t>状态</t>
+  </si>
+  <si>
+    <t>名额扣除类型</t>
   </si>
 </sst>
 </file>
@@ -565,30 +568,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AG1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.28515625" customWidth="1"/>
-    <col min="13" max="13" width="16.7109375" customWidth="1"/>
-    <col min="14" max="18" width="19.140625" customWidth="1"/>
-    <col min="19" max="19" width="21.42578125" customWidth="1"/>
-    <col min="20" max="23" width="19.140625" customWidth="1"/>
-    <col min="24" max="24" width="16.7109375" customWidth="1"/>
-    <col min="25" max="26" width="19.42578125" customWidth="1"/>
-    <col min="27" max="27" width="21.28515625" customWidth="1"/>
-    <col min="28" max="28" width="23.28515625" customWidth="1"/>
-    <col min="29" max="30" width="26.5703125" customWidth="1"/>
-    <col min="31" max="31" width="29.140625" customWidth="1"/>
-    <col min="32" max="32" width="27.85546875" customWidth="1"/>
+    <col min="7" max="8" width="12.7109375" customWidth="1"/>
+    <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.28515625" customWidth="1"/>
+    <col min="14" max="14" width="16.7109375" customWidth="1"/>
+    <col min="15" max="19" width="19.140625" customWidth="1"/>
+    <col min="20" max="20" width="21.42578125" customWidth="1"/>
+    <col min="21" max="24" width="19.140625" customWidth="1"/>
+    <col min="25" max="25" width="16.7109375" customWidth="1"/>
+    <col min="26" max="27" width="19.42578125" customWidth="1"/>
+    <col min="28" max="28" width="21.28515625" customWidth="1"/>
+    <col min="29" max="29" width="23.28515625" customWidth="1"/>
+    <col min="30" max="31" width="26.5703125" customWidth="1"/>
+    <col min="32" max="32" width="29.140625" customWidth="1"/>
+    <col min="33" max="33" width="27.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>9</v>
       </c>
@@ -611,78 +614,81 @@
         <v>4</v>
       </c>
       <c r="H1" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="W1" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="Y1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Z1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="AA1" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AB1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AC1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AD1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AE1" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AF1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AG1" s="3" t="s">
         <v>16</v>
       </c>
     </row>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23801"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{242EE13B-12BA-4F0D-AA6A-C24F768EC6AB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AE7652F-7AB8-4AAD-BE26-9AF2A56146E9}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="51">
   <si>
     <t>代理商</t>
   </si>
@@ -184,6 +184,9 @@
   </si>
   <si>
     <t>名额扣除类型</t>
+  </si>
+  <si>
+    <t>是否ZKB 599方案</t>
   </si>
 </sst>
 </file>
@@ -568,30 +571,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
-  <dimension ref="A1:AG1"/>
+  <dimension ref="A1:AH1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="12.7109375" customWidth="1"/>
-    <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.28515625" customWidth="1"/>
-    <col min="14" max="14" width="16.7109375" customWidth="1"/>
-    <col min="15" max="19" width="19.140625" customWidth="1"/>
-    <col min="20" max="20" width="21.42578125" customWidth="1"/>
-    <col min="21" max="24" width="19.140625" customWidth="1"/>
-    <col min="25" max="25" width="16.7109375" customWidth="1"/>
-    <col min="26" max="27" width="19.42578125" customWidth="1"/>
-    <col min="28" max="28" width="21.28515625" customWidth="1"/>
-    <col min="29" max="29" width="23.28515625" customWidth="1"/>
-    <col min="30" max="31" width="26.5703125" customWidth="1"/>
-    <col min="32" max="32" width="29.140625" customWidth="1"/>
-    <col min="33" max="33" width="27.85546875" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="12.7109375" customWidth="1"/>
+    <col min="11" max="11" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.28515625" customWidth="1"/>
+    <col min="15" max="15" width="16.7109375" customWidth="1"/>
+    <col min="16" max="20" width="19.140625" customWidth="1"/>
+    <col min="21" max="21" width="21.42578125" customWidth="1"/>
+    <col min="22" max="25" width="19.140625" customWidth="1"/>
+    <col min="26" max="26" width="16.7109375" customWidth="1"/>
+    <col min="27" max="28" width="19.42578125" customWidth="1"/>
+    <col min="29" max="29" width="21.28515625" customWidth="1"/>
+    <col min="30" max="30" width="23.28515625" customWidth="1"/>
+    <col min="31" max="32" width="26.5703125" customWidth="1"/>
+    <col min="33" max="33" width="29.140625" customWidth="1"/>
+    <col min="34" max="34" width="27.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:34" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>9</v>
       </c>
@@ -602,93 +605,96 @@
         <v>7</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="W1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="Y1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Z1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="AA1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AB1" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AC1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AD1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AE1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AF1" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AG1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="AG1" s="3" t="s">
+      <c r="AH1" s="3" t="s">
         <v>16</v>
       </c>
     </row>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AE7652F-7AB8-4AAD-BE26-9AF2A56146E9}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71FAF5C7-DF34-4A31-887C-AE6E9C7A3EC2}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
     <sheet name="合同" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="52">
   <si>
     <t>代理商</t>
   </si>
@@ -187,6 +187,9 @@
   </si>
   <si>
     <t>是否ZKB 599方案</t>
+  </si>
+  <si>
+    <t>是否代理商自身原因未完成培训</t>
   </si>
 </sst>
 </file>
@@ -779,7 +782,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1A9004E-0524-4CCC-A26D-ED41880F2076}">
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" customWidth="1"/>
@@ -790,10 +793,11 @@
     <col min="8" max="8" width="12.42578125" customWidth="1"/>
     <col min="9" max="9" width="13.5703125" customWidth="1"/>
     <col min="10" max="11" width="12.42578125" customWidth="1"/>
-    <col min="12" max="12" width="12.7109375" customWidth="1"/>
+    <col min="12" max="12" width="33.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>7</v>
       </c>
@@ -828,10 +832,13 @@
         <v>30</v>
       </c>
       <c r="L1" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="M1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M1" s="2"/>
       <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71FAF5C7-DF34-4A31-887C-AE6E9C7A3EC2}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B13CEEC-812D-4C37-8A24-C6CD7C4003DC}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
     <sheet name="合同" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="53">
   <si>
     <t>代理商</t>
   </si>
@@ -190,6 +190,9 @@
   </si>
   <si>
     <t>是否代理商自身原因未完成培训</t>
+  </si>
+  <si>
+    <t>ID</t>
   </si>
 </sst>
 </file>
@@ -795,6 +798,7 @@
     <col min="10" max="11" width="12.42578125" customWidth="1"/>
     <col min="12" max="12" width="33.85546875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12.7109375" customWidth="1"/>
+    <col min="14" max="14" width="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -837,7 +841,9 @@
       <c r="M1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="N1" s="2"/>
+      <c r="N1" s="3" t="s">
+        <v>52</v>
+      </c>
       <c r="O1" s="2"/>
     </row>
   </sheetData>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503277717\Desktop\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B13CEEC-812D-4C37-8A24-C6CD7C4003DC}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AA5A252-EE1D-494D-A836-E0C312326DDD}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" activeTab="2" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
     <sheet name="合同" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="54">
   <si>
     <t>代理商</t>
   </si>
@@ -193,24 +193,28 @@
   </si>
   <si>
     <t>ID</t>
+  </si>
+  <si>
+    <t>设备分类</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -218,6 +222,15 @@
       <sz val="12"/>
       <color rgb="FF172B4D"/>
       <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -265,7 +278,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -281,7 +294,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -578,29 +591,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
   <dimension ref="A1:AH1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.1" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="12.7109375" customWidth="1"/>
-    <col min="11" max="11" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.28515625" customWidth="1"/>
-    <col min="15" max="15" width="16.7109375" customWidth="1"/>
-    <col min="16" max="20" width="19.140625" customWidth="1"/>
-    <col min="21" max="21" width="21.42578125" customWidth="1"/>
-    <col min="22" max="25" width="19.140625" customWidth="1"/>
-    <col min="26" max="26" width="16.7109375" customWidth="1"/>
-    <col min="27" max="28" width="19.42578125" customWidth="1"/>
-    <col min="29" max="29" width="21.28515625" customWidth="1"/>
-    <col min="30" max="30" width="23.28515625" customWidth="1"/>
-    <col min="31" max="32" width="26.5703125" customWidth="1"/>
-    <col min="33" max="33" width="29.140625" customWidth="1"/>
-    <col min="34" max="34" width="27.85546875" customWidth="1"/>
+    <col min="5" max="5" width="9.84765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="12.69921875" customWidth="1"/>
+    <col min="11" max="11" width="9.84765625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.3984375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.69921875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.296875" customWidth="1"/>
+    <col min="15" max="15" width="16.69921875" customWidth="1"/>
+    <col min="16" max="20" width="19.1484375" customWidth="1"/>
+    <col min="21" max="21" width="21.3984375" customWidth="1"/>
+    <col min="22" max="25" width="19.1484375" customWidth="1"/>
+    <col min="26" max="26" width="16.69921875" customWidth="1"/>
+    <col min="27" max="28" width="19.3984375" customWidth="1"/>
+    <col min="29" max="29" width="21.296875" customWidth="1"/>
+    <col min="30" max="30" width="23.296875" customWidth="1"/>
+    <col min="31" max="32" width="26.546875" customWidth="1"/>
+    <col min="33" max="33" width="29.1484375" customWidth="1"/>
+    <col min="34" max="34" width="27.84765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:34" s="4" customFormat="1" ht="15.3" x14ac:dyDescent="0.5">
       <c r="A1" s="3" t="s">
         <v>9</v>
       </c>
@@ -705,6 +718,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -713,24 +727,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD4DBF4-FEF1-4385-BAD9-BD07A4FA541B}">
   <dimension ref="A1:O1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.1" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="15.85546875" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" customWidth="1"/>
-    <col min="5" max="5" width="16.42578125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.7109375" style="1" customWidth="1"/>
-    <col min="7" max="8" width="16.85546875" customWidth="1"/>
-    <col min="10" max="10" width="19.28515625" customWidth="1"/>
-    <col min="11" max="11" width="15.140625" customWidth="1"/>
-    <col min="12" max="12" width="15.85546875" customWidth="1"/>
+    <col min="1" max="1" width="15.84765625" customWidth="1"/>
+    <col min="2" max="2" width="13.296875" customWidth="1"/>
+    <col min="3" max="3" width="14.69921875" customWidth="1"/>
+    <col min="4" max="4" width="15.546875" customWidth="1"/>
+    <col min="5" max="5" width="16.3984375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.69921875" style="1" customWidth="1"/>
+    <col min="7" max="8" width="16.84765625" customWidth="1"/>
+    <col min="10" max="10" width="19.296875" customWidth="1"/>
+    <col min="11" max="11" width="15.1484375" customWidth="1"/>
+    <col min="12" max="12" width="15.84765625" customWidth="1"/>
     <col min="13" max="13" width="16" customWidth="1"/>
-    <col min="14" max="14" width="17.28515625" customWidth="1"/>
-    <col min="15" max="15" width="21.5703125" customWidth="1"/>
+    <col min="14" max="14" width="17.296875" customWidth="1"/>
+    <col min="15" max="15" width="21.546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="15.3" x14ac:dyDescent="0.5">
       <c r="A1" s="3" t="s">
         <v>9</v>
       </c>
@@ -778,6 +792,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -785,23 +800,23 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1A9004E-0524-4CCC-A26D-ED41880F2076}">
-  <dimension ref="A1:O1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:P1"/>
+  <sheetFormatPr defaultRowHeight="14.1" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" customWidth="1"/>
-    <col min="2" max="2" width="17.7109375" customWidth="1"/>
-    <col min="3" max="3" width="20.28515625" customWidth="1"/>
-    <col min="4" max="4" width="10.5703125" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" customWidth="1"/>
-    <col min="8" max="8" width="12.42578125" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" customWidth="1"/>
-    <col min="10" max="11" width="12.42578125" customWidth="1"/>
-    <col min="12" max="12" width="33.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.7109375" customWidth="1"/>
-    <col min="14" max="14" width="24" customWidth="1"/>
+    <col min="1" max="1" width="11.3984375" customWidth="1"/>
+    <col min="2" max="2" width="17.69921875" customWidth="1"/>
+    <col min="3" max="3" width="20.296875" customWidth="1"/>
+    <col min="4" max="4" width="10.546875" customWidth="1"/>
+    <col min="5" max="5" width="12.69921875" customWidth="1"/>
+    <col min="8" max="9" width="12.3984375" customWidth="1"/>
+    <col min="10" max="10" width="13.546875" customWidth="1"/>
+    <col min="11" max="12" width="12.3984375" customWidth="1"/>
+    <col min="13" max="13" width="33.84765625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.69921875" customWidth="1"/>
+    <col min="15" max="15" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="15.3" x14ac:dyDescent="0.5">
       <c r="A1" s="3" t="s">
         <v>7</v>
       </c>
@@ -827,26 +842,30 @@
         <v>13</v>
       </c>
       <c r="I1" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -855,16 +874,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9A2251D-DDD2-48AF-A0F7-E61944EE8578}">
   <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.1" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" customWidth="1"/>
-    <col min="4" max="4" width="20.140625" customWidth="1"/>
-    <col min="5" max="5" width="27.85546875" customWidth="1"/>
-    <col min="6" max="6" width="19.140625" customWidth="1"/>
+    <col min="3" max="3" width="15.69921875" customWidth="1"/>
+    <col min="4" max="4" width="20.1484375" customWidth="1"/>
+    <col min="5" max="5" width="27.84765625" customWidth="1"/>
+    <col min="6" max="6" width="19.1484375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="15.3" x14ac:dyDescent="0.5">
       <c r="A1" s="3" t="s">
         <v>7</v>
       </c>
@@ -885,6 +904,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503277717\Desktop\New folder\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AA5A252-EE1D-494D-A836-E0C312326DDD}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A48DFCD-54A8-4BC2-A492-1B34BCFB700D}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" activeTab="2" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
     <sheet name="合同" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="55">
   <si>
     <t>代理商</t>
   </si>
@@ -197,24 +197,27 @@
   <si>
     <t>设备分类</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否由GE FE提供年度1次现场保养</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -227,7 +230,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -278,7 +281,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -294,7 +297,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -591,29 +594,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
   <dimension ref="A1:AH1"/>
-  <sheetFormatPr defaultRowHeight="14.1" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="5" max="5" width="9.84765625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.3984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="12.69921875" customWidth="1"/>
-    <col min="11" max="11" width="9.84765625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.3984375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.69921875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.296875" customWidth="1"/>
-    <col min="15" max="15" width="16.69921875" customWidth="1"/>
-    <col min="16" max="20" width="19.1484375" customWidth="1"/>
-    <col min="21" max="21" width="21.3984375" customWidth="1"/>
-    <col min="22" max="25" width="19.1484375" customWidth="1"/>
-    <col min="26" max="26" width="16.69921875" customWidth="1"/>
-    <col min="27" max="28" width="19.3984375" customWidth="1"/>
-    <col min="29" max="29" width="21.296875" customWidth="1"/>
-    <col min="30" max="30" width="23.296875" customWidth="1"/>
-    <col min="31" max="32" width="26.546875" customWidth="1"/>
-    <col min="33" max="33" width="29.1484375" customWidth="1"/>
-    <col min="34" max="34" width="27.84765625" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="12.7109375" customWidth="1"/>
+    <col min="11" max="11" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.28515625" customWidth="1"/>
+    <col min="15" max="15" width="16.7109375" customWidth="1"/>
+    <col min="16" max="20" width="19.140625" customWidth="1"/>
+    <col min="21" max="21" width="21.42578125" customWidth="1"/>
+    <col min="22" max="25" width="19.140625" customWidth="1"/>
+    <col min="26" max="26" width="16.7109375" customWidth="1"/>
+    <col min="27" max="28" width="19.42578125" customWidth="1"/>
+    <col min="29" max="29" width="21.28515625" customWidth="1"/>
+    <col min="30" max="30" width="23.28515625" customWidth="1"/>
+    <col min="31" max="32" width="26.5703125" customWidth="1"/>
+    <col min="33" max="33" width="29.140625" customWidth="1"/>
+    <col min="34" max="34" width="27.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" s="4" customFormat="1" ht="15.3" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:34" s="4" customFormat="1">
       <c r="A1" s="3" t="s">
         <v>9</v>
       </c>
@@ -727,24 +730,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD4DBF4-FEF1-4385-BAD9-BD07A4FA541B}">
   <dimension ref="A1:O1"/>
-  <sheetFormatPr defaultRowHeight="14.1" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15.84765625" customWidth="1"/>
-    <col min="2" max="2" width="13.296875" customWidth="1"/>
-    <col min="3" max="3" width="14.69921875" customWidth="1"/>
-    <col min="4" max="4" width="15.546875" customWidth="1"/>
-    <col min="5" max="5" width="16.3984375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.69921875" style="1" customWidth="1"/>
-    <col min="7" max="8" width="16.84765625" customWidth="1"/>
-    <col min="10" max="10" width="19.296875" customWidth="1"/>
-    <col min="11" max="11" width="15.1484375" customWidth="1"/>
-    <col min="12" max="12" width="15.84765625" customWidth="1"/>
+    <col min="1" max="1" width="15.85546875" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" customWidth="1"/>
+    <col min="5" max="5" width="16.42578125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.7109375" style="1" customWidth="1"/>
+    <col min="7" max="8" width="16.85546875" customWidth="1"/>
+    <col min="10" max="10" width="19.28515625" customWidth="1"/>
+    <col min="11" max="11" width="15.140625" customWidth="1"/>
+    <col min="12" max="12" width="15.85546875" customWidth="1"/>
     <col min="13" max="13" width="16" customWidth="1"/>
-    <col min="14" max="14" width="17.296875" customWidth="1"/>
-    <col min="15" max="15" width="21.546875" customWidth="1"/>
+    <col min="14" max="14" width="17.28515625" customWidth="1"/>
+    <col min="15" max="15" width="21.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.3" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:15">
       <c r="A1" s="3" t="s">
         <v>9</v>
       </c>
@@ -800,23 +803,24 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1A9004E-0524-4CCC-A26D-ED41880F2076}">
-  <dimension ref="A1:P1"/>
-  <sheetFormatPr defaultRowHeight="14.1" x14ac:dyDescent="0.5"/>
+  <dimension ref="A1:Q1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.3984375" customWidth="1"/>
-    <col min="2" max="2" width="17.69921875" customWidth="1"/>
-    <col min="3" max="3" width="20.296875" customWidth="1"/>
-    <col min="4" max="4" width="10.546875" customWidth="1"/>
-    <col min="5" max="5" width="12.69921875" customWidth="1"/>
-    <col min="8" max="9" width="12.3984375" customWidth="1"/>
-    <col min="10" max="10" width="13.546875" customWidth="1"/>
-    <col min="11" max="12" width="12.3984375" customWidth="1"/>
-    <col min="13" max="13" width="33.84765625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.69921875" customWidth="1"/>
-    <col min="15" max="15" width="24" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="20.28515625" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" customWidth="1"/>
+    <col min="8" max="9" width="12.42578125" customWidth="1"/>
+    <col min="10" max="10" width="13.5703125" customWidth="1"/>
+    <col min="11" max="12" width="12.42578125" customWidth="1"/>
+    <col min="13" max="13" width="33.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="33.85546875" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" customWidth="1"/>
+    <col min="16" max="16" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15.3" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:17">
       <c r="A1" s="3" t="s">
         <v>7</v>
       </c>
@@ -857,12 +861,15 @@
         <v>51</v>
       </c>
       <c r="N1" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="O1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -874,16 +881,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9A2251D-DDD2-48AF-A0F7-E61944EE8578}">
   <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="14.1" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="15.69921875" customWidth="1"/>
-    <col min="4" max="4" width="20.1484375" customWidth="1"/>
-    <col min="5" max="5" width="27.84765625" customWidth="1"/>
-    <col min="6" max="6" width="19.1484375" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" customWidth="1"/>
+    <col min="4" max="4" width="20.140625" customWidth="1"/>
+    <col min="5" max="5" width="27.85546875" customWidth="1"/>
+    <col min="6" max="6" width="19.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.3" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:6">
       <c r="A1" s="3" t="s">
         <v>7</v>
       </c>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23801"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A48DFCD-54A8-4BC2-A492-1B34BCFB700D}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42FEF472-02D2-4D01-B3A1-96E245C719D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
     <sheet name="合同" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="56">
   <si>
     <t>代理商</t>
   </si>
@@ -200,6 +200,9 @@
   </si>
   <si>
     <t>是否由GE FE提供年度1次现场保养</t>
+  </si>
+  <si>
+    <t>公司编码</t>
   </si>
 </sst>
 </file>
@@ -593,7 +596,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
-  <dimension ref="A1:AH1"/>
+  <dimension ref="A1:AI1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
@@ -612,11 +615,11 @@
     <col min="29" max="29" width="21.28515625" customWidth="1"/>
     <col min="30" max="30" width="23.28515625" customWidth="1"/>
     <col min="31" max="32" width="26.5703125" customWidth="1"/>
-    <col min="33" max="33" width="29.140625" customWidth="1"/>
-    <col min="34" max="34" width="27.85546875" customWidth="1"/>
+    <col min="33" max="34" width="29.140625" customWidth="1"/>
+    <col min="35" max="35" width="27.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" s="4" customFormat="1">
+    <row r="1" spans="1:35" s="4" customFormat="1">
       <c r="A1" s="3" t="s">
         <v>9</v>
       </c>
@@ -717,6 +720,9 @@
         <v>25</v>
       </c>
       <c r="AH1" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="AI1" s="3" t="s">
         <v>16</v>
       </c>
     </row>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42FEF472-02D2-4D01-B3A1-96E245C719D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA07486C-C260-4AFD-A1C7-0338456E233B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="58">
   <si>
     <t>代理商</t>
   </si>
@@ -203,6 +203,12 @@
   </si>
   <si>
     <t>公司编码</t>
+  </si>
+  <si>
+    <t>599合同年份</t>
+  </si>
+  <si>
+    <t>关联合同号</t>
   </si>
 </sst>
 </file>
@@ -596,9 +602,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
-  <dimension ref="A1:AI1"/>
+  <dimension ref="A1:AK1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
+    <col min="4" max="4" width="18.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="14.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="12.7109375" customWidth="1"/>
@@ -615,11 +622,11 @@
     <col min="29" max="29" width="21.28515625" customWidth="1"/>
     <col min="30" max="30" width="23.28515625" customWidth="1"/>
     <col min="31" max="32" width="26.5703125" customWidth="1"/>
-    <col min="33" max="34" width="29.140625" customWidth="1"/>
-    <col min="35" max="35" width="27.85546875" customWidth="1"/>
+    <col min="33" max="36" width="29.140625" customWidth="1"/>
+    <col min="37" max="37" width="27.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" s="4" customFormat="1">
+    <row r="1" spans="1:37" s="4" customFormat="1">
       <c r="A1" s="3" t="s">
         <v>9</v>
       </c>
@@ -723,6 +730,12 @@
         <v>55</v>
       </c>
       <c r="AI1" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="AJ1" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="AK1" s="3" t="s">
         <v>16</v>
       </c>
     </row>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA07486C-C260-4AFD-A1C7-0338456E233B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38235290-19D1-4D8B-B155-0FD06D38F0D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
     <sheet name="合同" sheetId="1" r:id="rId1"/>
@@ -892,6 +892,17 @@
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L1048576" xr:uid="{68886B27-8190-4CC1-A37C-2694D24E2574}">
+      <formula1>"超声高端机,超声低端机,N/A,depot"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M1048576" xr:uid="{14E18709-A84F-4D1A-8AE3-5A0CBC8FBD95}">
+      <formula1>"N/A,是,否"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N1048576" xr:uid="{384D9217-6876-49E1-A172-32BADC916192}">
+      <formula1>"是,否"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38235290-19D1-4D8B-B155-0FD06D38F0D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43773958-FA9C-4ECF-874C-DAD83759CD31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
     <sheet name="合同" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="59">
   <si>
     <t>代理商</t>
   </si>
@@ -209,6 +209,9 @@
   </si>
   <si>
     <t>关联合同号</t>
+  </si>
+  <si>
+    <t>2022年起探头高低端名额分类</t>
   </si>
 </sst>
 </file>
@@ -602,31 +605,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
-  <dimension ref="A1:AK1"/>
+  <dimension ref="A1:AL1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="18.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="12.7109375" customWidth="1"/>
-    <col min="11" max="11" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.28515625" customWidth="1"/>
-    <col min="15" max="15" width="16.7109375" customWidth="1"/>
-    <col min="16" max="20" width="19.140625" customWidth="1"/>
-    <col min="21" max="21" width="21.42578125" customWidth="1"/>
-    <col min="22" max="25" width="19.140625" customWidth="1"/>
-    <col min="26" max="26" width="16.7109375" customWidth="1"/>
-    <col min="27" max="28" width="19.42578125" customWidth="1"/>
-    <col min="29" max="29" width="21.28515625" customWidth="1"/>
-    <col min="30" max="30" width="23.28515625" customWidth="1"/>
-    <col min="31" max="32" width="26.5703125" customWidth="1"/>
-    <col min="33" max="36" width="29.140625" customWidth="1"/>
-    <col min="37" max="37" width="27.85546875" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="31.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.28515625" customWidth="1"/>
+    <col min="16" max="16" width="16.7109375" customWidth="1"/>
+    <col min="17" max="21" width="19.140625" customWidth="1"/>
+    <col min="22" max="22" width="21.42578125" customWidth="1"/>
+    <col min="23" max="26" width="19.140625" customWidth="1"/>
+    <col min="27" max="27" width="16.7109375" customWidth="1"/>
+    <col min="28" max="29" width="19.42578125" customWidth="1"/>
+    <col min="30" max="30" width="21.28515625" customWidth="1"/>
+    <col min="31" max="31" width="23.28515625" customWidth="1"/>
+    <col min="32" max="33" width="26.5703125" customWidth="1"/>
+    <col min="34" max="37" width="29.140625" customWidth="1"/>
+    <col min="38" max="38" width="27.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="4" customFormat="1">
+    <row r="1" spans="1:38" s="4" customFormat="1">
       <c r="A1" s="3" t="s">
         <v>9</v>
       </c>
@@ -655,87 +660,90 @@
         <v>49</v>
       </c>
       <c r="J1" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="W1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="Y1" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Z1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="AA1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AB1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AC1" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AD1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AE1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AF1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AG1" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AG1" s="3" t="s">
+      <c r="AH1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="AH1" s="3" t="s">
+      <c r="AI1" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="AI1" s="3" t="s">
+      <c r="AJ1" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="AJ1" s="3" t="s">
+      <c r="AK1" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="AK1" s="3" t="s">
+      <c r="AL1" s="3" t="s">
         <v>16</v>
       </c>
     </row>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43773958-FA9C-4ECF-874C-DAD83759CD31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AD053DB-90B0-43EF-B039-E3A5198B719E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
     <sheet name="合同" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="67">
   <si>
     <t>代理商</t>
   </si>
@@ -212,6 +212,30 @@
   </si>
   <si>
     <t>2022年起探头高低端名额分类</t>
+  </si>
+  <si>
+    <t>保养剩余名额</t>
+  </si>
+  <si>
+    <t>保养申请名额</t>
+  </si>
+  <si>
+    <t>保养已使用名额</t>
+  </si>
+  <si>
+    <t>备件高值总额</t>
+  </si>
+  <si>
+    <t>保养总额</t>
+  </si>
+  <si>
+    <t>备件高值剩余名额</t>
+  </si>
+  <si>
+    <t>备件高值申请中名额</t>
+  </si>
+  <si>
+    <t>备件高值已使用名额</t>
   </si>
 </sst>
 </file>
@@ -605,7 +629,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
-  <dimension ref="A1:AL1"/>
+  <dimension ref="A1:AT1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="18.42578125" bestFit="1" customWidth="1"/>
@@ -627,11 +651,11 @@
     <col min="30" max="30" width="21.28515625" customWidth="1"/>
     <col min="31" max="31" width="23.28515625" customWidth="1"/>
     <col min="32" max="33" width="26.5703125" customWidth="1"/>
-    <col min="34" max="37" width="29.140625" customWidth="1"/>
-    <col min="38" max="38" width="27.85546875" customWidth="1"/>
+    <col min="34" max="45" width="29.140625" customWidth="1"/>
+    <col min="46" max="46" width="27.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" s="4" customFormat="1">
+    <row r="1" spans="1:46" s="4" customFormat="1">
       <c r="A1" s="3" t="s">
         <v>9</v>
       </c>
@@ -735,15 +759,39 @@
         <v>25</v>
       </c>
       <c r="AI1" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ1" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="AK1" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AL1" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="AM1" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="AN1" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="AO1" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AP1" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AQ1" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="AJ1" s="3" t="s">
+      <c r="AR1" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="AK1" s="3" t="s">
+      <c r="AS1" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="AL1" s="3" t="s">
+      <c r="AT1" s="3" t="s">
         <v>16</v>
       </c>
     </row>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Intellij Idea\codes\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503277717\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AD053DB-90B0-43EF-B039-E3A5198B719E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{927FB2E7-C4E3-44B4-9CAC-B8B91CC1EED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
     <sheet name="合同" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="68">
   <si>
     <t>代理商</t>
   </si>
@@ -236,6 +236,10 @@
   </si>
   <si>
     <t>备件高值已使用名额</t>
+  </si>
+  <si>
+    <t>合同金额</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -246,14 +250,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -266,7 +270,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -317,7 +321,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -333,7 +337,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -629,33 +633,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
-  <dimension ref="A1:AT1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:AU1"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="4" max="4" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="31.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.28515625" customWidth="1"/>
-    <col min="16" max="16" width="16.7109375" customWidth="1"/>
-    <col min="17" max="21" width="19.140625" customWidth="1"/>
-    <col min="22" max="22" width="21.42578125" customWidth="1"/>
-    <col min="23" max="26" width="19.140625" customWidth="1"/>
-    <col min="27" max="27" width="16.7109375" customWidth="1"/>
-    <col min="28" max="29" width="19.42578125" customWidth="1"/>
-    <col min="30" max="30" width="21.28515625" customWidth="1"/>
-    <col min="31" max="31" width="23.28515625" customWidth="1"/>
-    <col min="32" max="33" width="26.5703125" customWidth="1"/>
-    <col min="34" max="45" width="29.140625" customWidth="1"/>
-    <col min="46" max="46" width="27.85546875" customWidth="1"/>
+    <col min="5" max="6" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.7109375" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="31.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.28515625" customWidth="1"/>
+    <col min="17" max="17" width="16.7109375" customWidth="1"/>
+    <col min="18" max="22" width="19.140625" customWidth="1"/>
+    <col min="23" max="23" width="21.42578125" customWidth="1"/>
+    <col min="24" max="27" width="19.140625" customWidth="1"/>
+    <col min="28" max="28" width="16.7109375" customWidth="1"/>
+    <col min="29" max="30" width="19.42578125" customWidth="1"/>
+    <col min="31" max="31" width="21.28515625" customWidth="1"/>
+    <col min="32" max="32" width="23.28515625" customWidth="1"/>
+    <col min="33" max="34" width="26.5703125" customWidth="1"/>
+    <col min="35" max="46" width="29.140625" customWidth="1"/>
+    <col min="47" max="47" width="27.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" s="4" customFormat="1">
+    <row r="1" spans="1:47" s="4" customFormat="1" ht="15.3">
       <c r="A1" s="3" t="s">
         <v>9</v>
       </c>
@@ -672,126 +676,129 @@
         <v>1</v>
       </c>
       <c r="F1" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="W1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="Y1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Z1" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="AA1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AB1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AC1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AD1" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AE1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AF1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AG1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AG1" s="3" t="s">
+      <c r="AH1" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AH1" s="3" t="s">
+      <c r="AI1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="AI1" s="3" t="s">
+      <c r="AJ1" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="AJ1" s="3" t="s">
+      <c r="AK1" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="AK1" s="3" t="s">
+      <c r="AL1" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="AL1" s="3" t="s">
+      <c r="AM1" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="AM1" s="3" t="s">
+      <c r="AN1" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="AN1" s="3" t="s">
+      <c r="AO1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="AO1" s="3" t="s">
+      <c r="AP1" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="AP1" s="3" t="s">
+      <c r="AQ1" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="AQ1" s="3" t="s">
+      <c r="AR1" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="AR1" s="3" t="s">
+      <c r="AS1" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="AS1" s="3" t="s">
+      <c r="AT1" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="AT1" s="3" t="s">
+      <c r="AU1" s="3" t="s">
         <v>16</v>
       </c>
     </row>
@@ -805,7 +812,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD4DBF4-FEF1-4385-BAD9-BD07A4FA541B}">
   <dimension ref="A1:O1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="15.85546875" customWidth="1"/>
     <col min="2" max="2" width="13.28515625" customWidth="1"/>
@@ -822,7 +829,7 @@
     <col min="15" max="15" width="21.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" ht="15.3">
       <c r="A1" s="3" t="s">
         <v>9</v>
       </c>
@@ -879,7 +886,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1A9004E-0524-4CCC-A26D-ED41880F2076}">
   <dimension ref="A1:Q1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="11.42578125" customWidth="1"/>
     <col min="2" max="2" width="17.7109375" customWidth="1"/>
@@ -895,7 +902,7 @@
     <col min="16" max="16" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:17" ht="15.3">
       <c r="A1" s="3" t="s">
         <v>7</v>
       </c>
@@ -967,7 +974,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9A2251D-DDD2-48AF-A0F7-E61944EE8578}">
   <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="2" max="2" width="17" customWidth="1"/>
     <col min="3" max="3" width="15.7109375" customWidth="1"/>
@@ -976,7 +983,7 @@
     <col min="6" max="6" width="19.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" ht="15.3">
       <c r="A1" s="3" t="s">
         <v>7</v>
       </c>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\503277717\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Java Codes\company\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{927FB2E7-C4E3-44B4-9CAC-B8B91CC1EED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4298AA4E-13A4-45E9-9881-18C137ADF86C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12552" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13992" activeTab="2" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
     <sheet name="合同" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="69">
   <si>
     <t>代理商</t>
   </si>
@@ -240,6 +240,9 @@
   <si>
     <t>合同金额</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>zone</t>
   </si>
 </sst>
 </file>
@@ -250,14 +253,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -270,7 +273,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -321,7 +324,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -337,7 +340,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -634,29 +637,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
   <dimension ref="A1:AU1"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="4" max="4" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.7109375" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="31.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.28515625" customWidth="1"/>
-    <col min="17" max="17" width="16.7109375" customWidth="1"/>
-    <col min="18" max="22" width="19.140625" customWidth="1"/>
-    <col min="23" max="23" width="21.42578125" customWidth="1"/>
-    <col min="24" max="27" width="19.140625" customWidth="1"/>
-    <col min="28" max="28" width="16.7109375" customWidth="1"/>
-    <col min="29" max="30" width="19.42578125" customWidth="1"/>
-    <col min="31" max="31" width="21.28515625" customWidth="1"/>
-    <col min="32" max="32" width="23.28515625" customWidth="1"/>
-    <col min="33" max="34" width="26.5703125" customWidth="1"/>
-    <col min="35" max="46" width="29.140625" customWidth="1"/>
-    <col min="47" max="47" width="27.85546875" customWidth="1"/>
+    <col min="4" max="4" width="18.41796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9.83984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.41796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.68359375" customWidth="1"/>
+    <col min="10" max="10" width="14.83984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="31.41796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.83984375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.41796875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.68359375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.26171875" customWidth="1"/>
+    <col min="17" max="17" width="16.68359375" customWidth="1"/>
+    <col min="18" max="22" width="19.15625" customWidth="1"/>
+    <col min="23" max="23" width="21.41796875" customWidth="1"/>
+    <col min="24" max="27" width="19.15625" customWidth="1"/>
+    <col min="28" max="28" width="16.68359375" customWidth="1"/>
+    <col min="29" max="30" width="19.41796875" customWidth="1"/>
+    <col min="31" max="31" width="21.26171875" customWidth="1"/>
+    <col min="32" max="32" width="23.26171875" customWidth="1"/>
+    <col min="33" max="34" width="26.578125" customWidth="1"/>
+    <col min="35" max="46" width="29.15625" customWidth="1"/>
+    <col min="47" max="47" width="27.83984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:47" s="4" customFormat="1" ht="15.3">
@@ -812,21 +815,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD4DBF4-FEF1-4385-BAD9-BD07A4FA541B}">
   <dimension ref="A1:O1"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="15.85546875" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" customWidth="1"/>
-    <col min="5" max="5" width="16.42578125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.7109375" style="1" customWidth="1"/>
-    <col min="7" max="8" width="16.85546875" customWidth="1"/>
-    <col min="10" max="10" width="19.28515625" customWidth="1"/>
-    <col min="11" max="11" width="15.140625" customWidth="1"/>
-    <col min="12" max="12" width="15.85546875" customWidth="1"/>
+    <col min="1" max="1" width="15.83984375" customWidth="1"/>
+    <col min="2" max="2" width="13.26171875" customWidth="1"/>
+    <col min="3" max="3" width="14.68359375" customWidth="1"/>
+    <col min="4" max="4" width="15.578125" customWidth="1"/>
+    <col min="5" max="5" width="16.41796875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.68359375" style="1" customWidth="1"/>
+    <col min="7" max="8" width="16.83984375" customWidth="1"/>
+    <col min="10" max="10" width="19.26171875" customWidth="1"/>
+    <col min="11" max="11" width="15.15625" customWidth="1"/>
+    <col min="12" max="12" width="15.83984375" customWidth="1"/>
     <col min="13" max="13" width="16" customWidth="1"/>
-    <col min="14" max="14" width="17.28515625" customWidth="1"/>
-    <col min="15" max="15" width="21.5703125" customWidth="1"/>
+    <col min="14" max="14" width="17.26171875" customWidth="1"/>
+    <col min="15" max="15" width="21.578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.3">
@@ -885,24 +888,24 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1A9004E-0524-4CCC-A26D-ED41880F2076}">
-  <dimension ref="A1:Q1"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <dimension ref="A1:R1"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" customWidth="1"/>
-    <col min="2" max="2" width="17.7109375" customWidth="1"/>
-    <col min="3" max="3" width="20.28515625" customWidth="1"/>
-    <col min="4" max="4" width="10.5703125" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" customWidth="1"/>
-    <col min="8" max="9" width="12.42578125" customWidth="1"/>
-    <col min="10" max="10" width="13.5703125" customWidth="1"/>
-    <col min="11" max="12" width="12.42578125" customWidth="1"/>
-    <col min="13" max="13" width="33.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="33.85546875" customWidth="1"/>
-    <col min="15" max="15" width="12.7109375" customWidth="1"/>
-    <col min="16" max="16" width="24" customWidth="1"/>
+    <col min="1" max="1" width="11.41796875" customWidth="1"/>
+    <col min="2" max="2" width="17.68359375" customWidth="1"/>
+    <col min="3" max="3" width="20.26171875" customWidth="1"/>
+    <col min="4" max="4" width="10.578125" customWidth="1"/>
+    <col min="5" max="5" width="12.68359375" customWidth="1"/>
+    <col min="8" max="9" width="12.41796875" customWidth="1"/>
+    <col min="10" max="10" width="13.578125" customWidth="1"/>
+    <col min="11" max="12" width="12.41796875" customWidth="1"/>
+    <col min="13" max="13" width="33.83984375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="33.83984375" customWidth="1"/>
+    <col min="15" max="16" width="12.68359375" customWidth="1"/>
+    <col min="17" max="17" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.3">
+    <row r="1" spans="1:18" ht="15.3">
       <c r="A1" s="3" t="s">
         <v>7</v>
       </c>
@@ -949,9 +952,12 @@
         <v>16</v>
       </c>
       <c r="P1" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q1" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -974,13 +980,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9A2251D-DDD2-48AF-A0F7-E61944EE8578}">
   <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" customWidth="1"/>
-    <col min="4" max="4" width="20.140625" customWidth="1"/>
-    <col min="5" max="5" width="27.85546875" customWidth="1"/>
-    <col min="6" max="6" width="19.140625" customWidth="1"/>
+    <col min="3" max="3" width="15.68359375" customWidth="1"/>
+    <col min="4" max="4" width="20.15625" customWidth="1"/>
+    <col min="5" max="5" width="27.83984375" customWidth="1"/>
+    <col min="6" max="6" width="19.15625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.3">

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Java Codes\company\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4298AA4E-13A4-45E9-9881-18C137ADF86C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28854165-C4CF-4AD1-91F6-20C0C482C1CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13992" activeTab="2" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13992" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
   <sheets>
     <sheet name="合同" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="74">
   <si>
     <t>代理商</t>
   </si>
@@ -243,6 +243,21 @@
   </si>
   <si>
     <t>zone</t>
+  </si>
+  <si>
+    <t>耗材总额</t>
+  </si>
+  <si>
+    <t>耗材剩余名额</t>
+  </si>
+  <si>
+    <t>耗材申请中名额</t>
+  </si>
+  <si>
+    <t>耗材已使用名额</t>
+  </si>
+  <si>
+    <t>耗材增幅</t>
   </si>
 </sst>
 </file>
@@ -340,9 +355,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主题">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -380,7 +395,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -486,7 +501,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -628,7 +643,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -636,7 +651,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
-  <dimension ref="A1:AU1"/>
+  <dimension ref="A1:AZ1"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="4" max="4" width="18.41796875" bestFit="1" customWidth="1"/>
@@ -650,7 +665,9 @@
     <col min="15" max="15" width="16.68359375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="13.26171875" customWidth="1"/>
     <col min="17" max="17" width="16.68359375" customWidth="1"/>
-    <col min="18" max="22" width="19.15625" customWidth="1"/>
+    <col min="18" max="19" width="19.15625" customWidth="1"/>
+    <col min="20" max="20" width="14.41796875" customWidth="1"/>
+    <col min="21" max="22" width="19.15625" customWidth="1"/>
     <col min="23" max="23" width="21.41796875" customWidth="1"/>
     <col min="24" max="27" width="19.15625" customWidth="1"/>
     <col min="28" max="28" width="16.68359375" customWidth="1"/>
@@ -658,11 +675,24 @@
     <col min="31" max="31" width="21.26171875" customWidth="1"/>
     <col min="32" max="32" width="23.26171875" customWidth="1"/>
     <col min="33" max="34" width="26.578125" customWidth="1"/>
-    <col min="35" max="46" width="29.15625" customWidth="1"/>
-    <col min="47" max="47" width="27.83984375" customWidth="1"/>
+    <col min="35" max="35" width="29.15625" customWidth="1"/>
+    <col min="36" max="36" width="9.9453125" customWidth="1"/>
+    <col min="37" max="37" width="14.05078125" customWidth="1"/>
+    <col min="38" max="38" width="14.3125" customWidth="1"/>
+    <col min="39" max="39" width="16.89453125" customWidth="1"/>
+    <col min="40" max="40" width="14.47265625" customWidth="1"/>
+    <col min="41" max="41" width="18.47265625" customWidth="1"/>
+    <col min="42" max="42" width="19.62890625" customWidth="1"/>
+    <col min="43" max="43" width="19.7890625" customWidth="1"/>
+    <col min="44" max="44" width="10.62890625" customWidth="1"/>
+    <col min="45" max="45" width="14" customWidth="1"/>
+    <col min="46" max="46" width="16.62890625" customWidth="1"/>
+    <col min="47" max="48" width="16" customWidth="1"/>
+    <col min="49" max="51" width="29.15625" customWidth="1"/>
+    <col min="52" max="52" width="27.83984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" s="4" customFormat="1" ht="15.3">
+    <row r="1" spans="1:52" s="4" customFormat="1" ht="15.3">
       <c r="A1" s="3" t="s">
         <v>9</v>
       </c>
@@ -793,15 +823,30 @@
         <v>66</v>
       </c>
       <c r="AR1" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="AS1" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="AT1" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="AU1" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="AV1" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="AW1" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="AS1" s="3" t="s">
+      <c r="AX1" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="AT1" s="3" t="s">
+      <c r="AY1" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="AU1" s="3" t="s">
+      <c r="AZ1" s="3" t="s">
         <v>16</v>
       </c>
     </row>

--- a/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
+++ b/src/src/main/webapp/portal/zkb/contract/excel/APM_ZKB_Contract_Exp_Template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Java Codes\company\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\JavaCodes\company\hc-apm-web\src\src\main\webapp\portal\zkb\contract\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28854165-C4CF-4AD1-91F6-20C0C482C1CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46A1D0F0-EAB1-4986-B905-44E7E02A689E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13992" xr2:uid="{DFA98752-8825-45D1-95EF-55416474EBE9}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="75">
   <si>
     <t>代理商</t>
   </si>
@@ -258,6 +258,9 @@
   </si>
   <si>
     <t>耗材增幅</t>
+  </si>
+  <si>
+    <t>是否可以申请工具箱</t>
   </si>
 </sst>
 </file>
@@ -651,7 +654,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C52200B-3B0C-4F93-BC6C-7CAE122E49C2}">
-  <dimension ref="A1:AZ1"/>
+  <dimension ref="A1:BA1"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="4" max="4" width="18.41796875" bestFit="1" customWidth="1"/>
@@ -688,11 +691,11 @@
     <col min="45" max="45" width="14" customWidth="1"/>
     <col min="46" max="46" width="16.62890625" customWidth="1"/>
     <col min="47" max="48" width="16" customWidth="1"/>
-    <col min="49" max="51" width="29.15625" customWidth="1"/>
-    <col min="52" max="52" width="27.83984375" customWidth="1"/>
+    <col min="49" max="52" width="29.15625" customWidth="1"/>
+    <col min="53" max="53" width="27.83984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:52" s="4" customFormat="1" ht="15.3">
+    <row r="1" spans="1:53" s="4" customFormat="1" ht="15.3">
       <c r="A1" s="3" t="s">
         <v>9</v>
       </c>
@@ -844,9 +847,12 @@
         <v>56</v>
       </c>
       <c r="AY1" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AZ1" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="AZ1" s="3" t="s">
+      <c r="BA1" s="3" t="s">
         <v>16</v>
       </c>
     </row>
